--- a/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -8,7 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="주간실적입력" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="주간보고내용" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="주간실적입력" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <r>
       <rPr>
@@ -51,7 +52,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">점검 주간 실적 보고</t>
+      <t xml:space="preserve">점검 주간 업무 보고</t>
     </r>
   </si>
   <si>
@@ -61,7 +62,47 @@
     <t xml:space="preserve">내가시스템</t>
   </si>
   <si>
-    <t xml:space="preserve">※ 수정하지 마세요</t>
+    <t xml:space="preserve">보고자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성명</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">기준일자</t>
@@ -113,11 +154,27 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: 2026-07-03</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 매주 목요일 날짜 입력</t>
+      <t xml:space="preserve">: 2026-07-10 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매주 목요일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">보고기간</t>
@@ -126,7 +183,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF0000FF"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -136,16 +193,16 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -155,34 +212,357 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전주 금요일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">~ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금주 목요일</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 기준일자 입력 후 자동 표시</t>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 2026-07-04 ~ 2026-07-10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사업기간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'26.6.26. ~ '26.11.15.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 금주 실적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금주 추진 내용을 자유롭게 작성하세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">착수보고회 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스마트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KAIS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 계정 요청
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지자체별 점검수량 파악</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 추진계획</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차주 계획을 작성하세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현장조사팀 배정
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현장 점검 시작</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 기타</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">특이사항 등</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지역별 주간 점검 실적 입력</t>
   </si>
   <si>
     <r>
@@ -190,16 +570,48 @@
         <b val="true"/>
         <sz val="9"/>
         <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">▶ 파란색 칸</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">▶ '</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
         <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금주점검건수</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">칸만 입력하세요 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -214,7 +626,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">금주점검건수</t>
+      <t xml:space="preserve">착수 초기에는 </t>
     </r>
     <r>
       <rPr>
@@ -225,7 +637,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">0 </t>
     </r>
     <r>
       <rPr>
@@ -235,7 +647,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정상</t>
+      <t xml:space="preserve">그대로 저장해도 됩니다</t>
     </r>
     <r>
       <rPr>
@@ -246,13 +658,36 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 정상</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -260,306 +695,250 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">망실</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">망실은 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KAIS </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설치현황 파일 업로드 시 자동 집계됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">여기서는 입력 불필요</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시군구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체대상건수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금주점검건수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경기도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">김포시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">성남시 분당구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">성남시 수정구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">성남시 중원구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서울특별시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금천구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서대문구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영등포구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">합 계</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 파일명 형식</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: [</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내가시스템</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기초번호판설치점검</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주간보고</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_YYYYMMDD.xlsx  (</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매주 목요일</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 입력하세요</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나머지는 수정하지 마세요</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시군구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체대상건수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금주점검건수</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">누적점검건수</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">참고</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">정상</t>
-  </si>
-  <si>
-    <t xml:space="preserve">훼손</t>
-  </si>
-  <si>
-    <t xml:space="preserve">망실</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경기도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">김포시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">→ 시스템 자동계산</t>
-  </si>
-  <si>
-    <t xml:space="preserve">성남시 분당구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">성남시 수정구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">성남시 중원구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">서울특별시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금천구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">서대문구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">영등포구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">합 계</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 파일명 형식</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: [</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내가시스템</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기초번호판설치점검</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주간보고</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_YYYYMMDD.xlsx  (</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">날짜는 매주 목요일</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 20260703)</t>
     </r>
   </si>
 </sst>
@@ -571,7 +950,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,13 +1001,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="맑은 고딕"/>
@@ -650,8 +1022,15 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF9C5700"/>
+      <sz val="11"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -665,6 +1044,28 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF9C5700"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="맑은 고딕"/>
@@ -681,13 +1082,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF9AA6B5"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -735,6 +1129,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
@@ -751,14 +1151,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -794,6 +1188,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -837,27 +1242,39 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -865,7 +1282,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -873,43 +1290,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -971,7 +1376,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF9AA6B5"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1165,15 +1570,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1185,11 +1586,8 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1199,345 +1597,421 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="4" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F12"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F24"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>1959</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>11119</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="A7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>1959</v>
-      </c>
-      <c r="E7" s="13" t="n">
+      <c r="E8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="13" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="E9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>163</v>
+      </c>
+      <c r="E10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="13" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>211</v>
+      </c>
+      <c r="E11" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>11119</v>
-      </c>
-      <c r="E8" s="13" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21" t="n">
+        <f aca="false">SUM(D5:D11)</f>
+        <v>13995</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <f aca="false">SUM(E5:E11)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>163</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>211</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20" t="n">
-        <f aca="false">SUM(D7:D13)</f>
-        <v>13995</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <f aca="false">SUM(E7:E13)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="20" t="n">
-        <f aca="false">SUM(G7:G13)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <f aca="false">SUM(H7:H13)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <f aca="false">SUM(I7:I13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A16:I16"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E56FC05-36FC-4C54-B0EC-0667A36AE23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424AAB29-8AF5-428A-84D5-DF2D72FF2A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,6 +255,12 @@
     <t>□ 금주 실적</t>
   </si>
   <si>
+    <t>□ 추진계획</t>
+  </si>
+  <si>
+    <t>□ 기타</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -291,678 +297,523 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>금주 추진 내용을 자유롭게 작성하세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">.
+      <t>특이사항 등</t>
+    </r>
+  </si>
+  <si>
+    <t>지역별 주간 점검 실적 입력</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>▶ '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>금주점검건수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">칸만 입력하세요 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">착수 초기에는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>그대로 저장해도 됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>※ 정상</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>훼손</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">망실은 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">KAIS </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>설치현황 파일 업로드 시 자동 집계됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>여기서는 입력 불필요</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>시도</t>
+  </si>
+  <si>
+    <t>시군구</t>
+  </si>
+  <si>
+    <t>전체대상건수</t>
+  </si>
+  <si>
+    <t>금주점검건수</t>
+  </si>
+  <si>
+    <t>경기도</t>
+  </si>
+  <si>
+    <t>김포시</t>
+  </si>
+  <si>
+    <t>성남시 분당구</t>
+  </si>
+  <si>
+    <t>성남시 수정구</t>
+  </si>
+  <si>
+    <t>성남시 중원구</t>
+  </si>
+  <si>
+    <t>서울특별시</t>
+  </si>
+  <si>
+    <t>금천구</t>
+  </si>
+  <si>
+    <t>서대문구</t>
+  </si>
+  <si>
+    <t>영등포구</t>
+  </si>
+  <si>
+    <t>합 계</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>※ 파일명 형식</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>: [</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>내가시스템</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>기초번호판설치점검</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>주간보고</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>_YYYYMMDD.xlsx  (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>매주 목요일</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[입력] 금주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내용을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자유롭게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">작성하세요.
 </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">착수보고회 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">월 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>스마트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">KAIS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 계정 요청
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[입력] 차주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계획을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">작성하세요.
 </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>지자체별 점검수량 파악</t>
-    </r>
-  </si>
-  <si>
-    <t>□ 추진계획</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>입력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>차주 계획을 작성하세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현장조사팀 배정
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>현장 점검 시작</t>
-    </r>
-  </si>
-  <si>
-    <t>□ 기타</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>입력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>특이사항 등</t>
-    </r>
-  </si>
-  <si>
-    <t>지역별 주간 점검 실적 입력</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>▶ '</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>금주점검건수</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">칸만 입력하세요 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">착수 초기에는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>그대로 저장해도 됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>※ 정상</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>훼손</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">망실은 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">KAIS </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>설치현황 파일 업로드 시 자동 집계됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>여기서는 입력 불필요</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>시도</t>
-  </si>
-  <si>
-    <t>시군구</t>
-  </si>
-  <si>
-    <t>전체대상건수</t>
-  </si>
-  <si>
-    <t>금주점검건수</t>
-  </si>
-  <si>
-    <t>경기도</t>
-  </si>
-  <si>
-    <t>김포시</t>
-  </si>
-  <si>
-    <t>성남시 분당구</t>
-  </si>
-  <si>
-    <t>성남시 수정구</t>
-  </si>
-  <si>
-    <t>성남시 중원구</t>
-  </si>
-  <si>
-    <t>서울특별시</t>
-  </si>
-  <si>
-    <t>금천구</t>
-  </si>
-  <si>
-    <t>서대문구</t>
-  </si>
-  <si>
-    <t>영등포구</t>
-  </si>
-  <si>
-    <t>합 계</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>※ 파일명 형식</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>: [</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>내가시스템</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>기초번호판설치점검</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>주간보고</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>_YYYYMMDD.xlsx  (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>날짜</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>매주 목요일</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)</t>
-    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1109,6 +960,12 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1241,24 +1098,21 @@
     <xf numFmtId="3" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1272,6 +1126,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1544,214 +1401,209 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1">
+      <c r="A14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" spans="1:6" ht="79.5" customHeight="1">
+      <c r="A15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1">
+      <c r="A20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" spans="1:6" ht="79.5" customHeight="1">
+      <c r="A21" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
     <mergeCell ref="B6:F6"/>
@@ -1759,6 +1611,11 @@
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1778,47 +1635,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
+      <c r="A2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1">
+      <c r="A3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="27.75" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1826,10 +1683,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6">
         <v>1959</v>
@@ -1843,10 +1700,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="D6" s="10">
         <v>11119</v>
@@ -1860,10 +1717,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="6">
         <v>450</v>
@@ -1877,10 +1734,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" s="10">
         <v>20</v>
@@ -1894,10 +1751,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D9" s="6">
         <v>73</v>
@@ -1911,10 +1768,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="D10" s="10">
         <v>163</v>
@@ -1928,10 +1785,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="6">
         <v>211</v>
@@ -1941,11 +1798,11 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
+      <c r="A12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="11">
         <f>SUM(D5:D11)</f>
         <v>13995</v>
@@ -1956,13 +1813,13 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
+      <c r="A14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaScript DEV\public-보고서\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaScript DEV\public-보고서\서버에 업로드_20260819_현재\addr.chk.2026-main\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E9E567-3E21-4432-B3EF-3AFB012346A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30495" yWindow="1245" windowWidth="24705" windowHeight="13470" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>

--- a/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaScript DEV\public-보고서\서버에 업로드_20260819_현재\addr.chk.2026-main\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E9E567-3E21-4432-B3EF-3AFB012346A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5FA866-4397-46F3-B23C-2B1947B830A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>
@@ -123,12 +123,6 @@
     <t>[입력] 성명</t>
   </si>
   <si>
-    <t>[입력] 예: 2026-07-10 (매주 목요일)</t>
-  </si>
-  <si>
-    <t>[입력] 예: 2026-07-04 ~ 2026-07-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">[입력] 금주 추진 내용을 자유롭게 작성하세요.
 </t>
     <phoneticPr fontId="9" type="noConversion"/>
@@ -149,6 +143,14 @@
   </si>
   <si>
     <t>※ 파일명 형식: [내가시스템]기초번호판설치점검_주간보고_YYYYMMDD.xlsx  (날짜=매주 목요일)</t>
+  </si>
+  <si>
+    <t>[입력] 예: 2026-08-20 (매주 목요일 기준으로 날짜 작성)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[입력] 예: 2026-08-14 ~ 2026-08-20</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -382,6 +384,21 @@
     <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -395,21 +412,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -683,209 +685,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
+      <c r="B5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-    </row>
-    <row r="15" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
     <mergeCell ref="B6:F6"/>
@@ -893,11 +900,6 @@
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F18"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -918,31 +920,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="A2" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="A3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1081,11 +1083,11 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="3">
         <f>SUM(D5:D11)</f>
         <v>13930</v>
@@ -1096,13 +1098,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="A14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
